--- a/algorithm/projects/数据融合/prod/docs/需求/需求材料/多光谱拼图需求 0908评估.xlsx
+++ b/algorithm/projects/数据融合/prod/docs/需求/需求材料/多光谱拼图需求 0908评估.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="24460"/>
+    <workbookView windowWidth="21520" windowHeight="24440"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
